--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Chumphon (CP)</t>
@@ -587,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -613,9 +616,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,13 +710,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>9.72503818011114</v>
@@ -754,12 +761,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>9.955535090435168</v>
@@ -801,12 +808,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>9.902911681069856</v>
@@ -848,12 +855,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>9.891163961190241</v>
@@ -895,12 +902,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>9.899089818316044</v>
@@ -942,12 +949,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>9.772629999999999</v>
@@ -989,12 +996,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>9.593045473378172</v>
@@ -1036,12 +1043,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>9.362117171706563</v>
@@ -1083,12 +1090,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>9.353183713500382</v>
@@ -1130,12 +1137,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>9.331050481889823</v>
@@ -1177,12 +1184,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>9.132160000000001</v>
@@ -1224,12 +1231,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>8.801550000000001</v>
@@ -1271,12 +1278,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>8.864663885579915</v>
@@ -1318,12 +1325,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>8.97315512281069</v>
@@ -1365,12 +1372,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>8.965900711787208</v>
@@ -1414,10 +1421,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>8.839505327391917</v>
@@ -1461,10 +1468,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>8.69168</v>
@@ -1508,10 +1515,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>8.822777230110802</v>
@@ -1555,10 +1562,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>8.304532560072531</v>
@@ -1602,10 +1609,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>8.146005101724441</v>
@@ -1649,10 +1656,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22">
         <v>8.067236836446714</v>
@@ -1696,10 +1703,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>8.035467017892126</v>
@@ -1743,10 +1750,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>7.902086117607117</v>
@@ -1790,10 +1797,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25">
         <v>7.932730656174178</v>
@@ -1837,10 +1844,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26">
         <v>7.40716</v>
@@ -1881,10 +1888,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27">
         <v>6.840862</v>
@@ -1928,10 +1935,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28">
         <v>7.44647</v>
@@ -1975,10 +1982,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29">
         <v>7.327537992062457</v>
@@ -2022,10 +2029,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30">
         <v>7.385103015863163</v>
@@ -2069,10 +2076,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31">
         <v>7.693113177702969</v>
@@ -2116,10 +2123,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C32">
         <v>5.847384</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
   <si>
     <t>location</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>YL1</t>
+  </si>
+  <si>
+    <t>Sandstone</t>
+  </si>
+  <si>
+    <t>Granite</t>
   </si>
 </sst>
 </file>
@@ -727,6 +733,12 @@
       <c r="D2">
         <v>99.11142670200115</v>
       </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2">
+        <v>50</v>
+      </c>
       <c r="J2">
         <v>7.8</v>
       </c>
@@ -774,6 +786,12 @@
       <c r="D3">
         <v>98.65486129056352</v>
       </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3">
+        <v>65</v>
+      </c>
       <c r="J3">
         <v>8.300000000000001</v>
       </c>
@@ -821,6 +839,12 @@
       <c r="D4">
         <v>98.63513166475543</v>
       </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4">
+        <v>40</v>
+      </c>
       <c r="J4">
         <v>8.300000000000001</v>
       </c>
@@ -868,6 +892,12 @@
       <c r="D5">
         <v>98.64453954257856</v>
       </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
       <c r="J5">
         <v>8.4</v>
       </c>
@@ -915,6 +945,12 @@
       <c r="D6">
         <v>98.65602411095496</v>
       </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
       <c r="J6">
         <v>8.199999999999999</v>
       </c>
@@ -962,6 +998,12 @@
       <c r="D7">
         <v>98.6005</v>
       </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7">
+        <v>46</v>
+      </c>
       <c r="J7">
         <v>8.300000000000001</v>
       </c>
@@ -1009,6 +1051,12 @@
       <c r="D8">
         <v>98.73398220094656</v>
       </c>
+      <c r="F8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8">
+        <v>75</v>
+      </c>
       <c r="J8">
         <v>8.1</v>
       </c>
@@ -1056,6 +1104,12 @@
       <c r="D9">
         <v>99.19222661016902</v>
       </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H9">
+        <v>45</v>
+      </c>
       <c r="J9">
         <v>7.7</v>
       </c>
@@ -1103,6 +1157,12 @@
       <c r="D10">
         <v>99.18685769168852</v>
       </c>
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10">
+        <v>40</v>
+      </c>
       <c r="J10">
         <v>7.8</v>
       </c>
@@ -1150,6 +1210,12 @@
       <c r="D11">
         <v>99.20409342147371</v>
       </c>
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
       <c r="J11">
         <v>7.9</v>
       </c>
@@ -1197,6 +1263,12 @@
       <c r="D12">
         <v>99.50174</v>
       </c>
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12">
+        <v>41</v>
+      </c>
       <c r="J12">
         <v>8.300000000000001</v>
       </c>
@@ -1244,6 +1316,12 @@
       <c r="D13">
         <v>99.4173</v>
       </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13">
+        <v>42</v>
+      </c>
       <c r="J13">
         <v>8.4</v>
       </c>
@@ -1291,6 +1369,12 @@
       <c r="D14">
         <v>99.03203141965326</v>
       </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14">
+        <v>53</v>
+      </c>
       <c r="J14">
         <v>8.1</v>
       </c>
@@ -1338,6 +1422,12 @@
       <c r="D15">
         <v>99.26761591472544</v>
       </c>
+      <c r="F15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
       <c r="J15">
         <v>7.9</v>
       </c>
@@ -1385,6 +1475,12 @@
       <c r="D16">
         <v>99.2802464362168</v>
       </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16">
+        <v>56</v>
+      </c>
       <c r="J16">
         <v>7.2</v>
       </c>
@@ -1432,6 +1528,12 @@
       <c r="D17">
         <v>99.22686870433924</v>
       </c>
+      <c r="F17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17">
+        <v>62</v>
+      </c>
       <c r="J17">
         <v>6.8</v>
       </c>
@@ -1479,6 +1581,12 @@
       <c r="D18">
         <v>98.4678</v>
       </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18">
+        <v>78</v>
+      </c>
       <c r="J18">
         <v>7.8</v>
       </c>
@@ -1526,6 +1634,12 @@
       <c r="D19">
         <v>98.43502089972058</v>
       </c>
+      <c r="F19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19">
+        <v>55</v>
+      </c>
       <c r="J19">
         <v>6.8</v>
       </c>
@@ -1573,6 +1687,12 @@
       <c r="D20">
         <v>98.27801528849022</v>
       </c>
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+      <c r="H20">
+        <v>45</v>
+      </c>
       <c r="J20">
         <v>6.9</v>
       </c>
@@ -1620,6 +1740,12 @@
       <c r="D21">
         <v>98.99656861576196</v>
       </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21">
+        <v>45</v>
+      </c>
       <c r="J21">
         <v>7.2</v>
       </c>
@@ -1667,6 +1793,12 @@
       <c r="D22">
         <v>99.00166090256778</v>
       </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22">
+        <v>47</v>
+      </c>
       <c r="J22">
         <v>7.3</v>
       </c>
@@ -1714,6 +1846,12 @@
       <c r="D23">
         <v>99.0949453609656</v>
       </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
       <c r="J23">
         <v>7.2</v>
       </c>
@@ -1761,6 +1899,12 @@
       <c r="D24">
         <v>99.11185263377725</v>
       </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24">
+        <v>47</v>
+      </c>
       <c r="J24">
         <v>7.2</v>
       </c>
@@ -1808,6 +1952,12 @@
       <c r="D25">
         <v>99.21022993424634</v>
       </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25">
+        <v>47</v>
+      </c>
       <c r="J25">
         <v>7</v>
       </c>
@@ -1855,6 +2005,12 @@
       <c r="D26">
         <v>99.46569</v>
       </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26">
+        <v>52</v>
+      </c>
       <c r="J26">
         <v>7.1</v>
       </c>
@@ -1899,6 +2055,12 @@
       <c r="D27">
         <v>100.15883</v>
       </c>
+      <c r="F27" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
       <c r="J27">
         <v>7.7</v>
       </c>
@@ -1946,6 +2108,12 @@
       <c r="D28">
         <v>100.13363</v>
       </c>
+      <c r="F28" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28">
+        <v>57</v>
+      </c>
       <c r="J28">
         <v>8</v>
       </c>
@@ -1993,6 +2161,12 @@
       <c r="D29">
         <v>99.98701242956552</v>
       </c>
+      <c r="F29" t="s">
+        <v>71</v>
+      </c>
+      <c r="H29">
+        <v>46</v>
+      </c>
       <c r="J29">
         <v>8</v>
       </c>
@@ -2040,6 +2214,12 @@
       <c r="D30">
         <v>99.9467856697036</v>
       </c>
+      <c r="F30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
+      </c>
       <c r="J30">
         <v>6.9</v>
       </c>
@@ -2087,6 +2267,12 @@
       <c r="D31">
         <v>100.0487368920784</v>
       </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31">
+        <v>41</v>
+      </c>
       <c r="J31">
         <v>7.7</v>
       </c>
@@ -2133,6 +2319,12 @@
       </c>
       <c r="D32">
         <v>101.074805</v>
+      </c>
+      <c r="F32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32">
+        <v>80</v>
       </c>
       <c r="J32">
         <v>7.8</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/THAILAND_Datenbank/after_conversion_thailand_mapped_readable.xlsx
@@ -610,8 +610,8 @@
     <col min="10" max="10" width="5.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" customWidth="1"/>
     <col min="12" max="12" width="34.7109375" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" customWidth="1"/>
-    <col min="15" max="19" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="19" width="20.7109375" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" customWidth="1"/>
     <col min="21" max="21" width="20.7109375" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" customWidth="1"/>
@@ -743,7 +743,10 @@
         <v>7.8</v>
       </c>
       <c r="L2">
-        <v>12.67875797281028</v>
+        <v>15.44085619137003</v>
+      </c>
+      <c r="N2">
+        <v>2.762098218559743</v>
       </c>
       <c r="O2">
         <v>1.226085167660975</v>
@@ -796,7 +799,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L3">
-        <v>4.493714923381924</v>
+        <v>6.598999234851081</v>
+      </c>
+      <c r="N3">
+        <v>2.105284311469158</v>
       </c>
       <c r="O3">
         <v>0.0008228759514503</v>
@@ -849,7 +855,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L4">
-        <v>5.11273774036931</v>
+        <v>7.131026832356272</v>
+      </c>
+      <c r="N4">
+        <v>2.018289091986962</v>
       </c>
       <c r="O4">
         <v>0.0012343139271754</v>
@@ -902,7 +911,10 @@
         <v>8.4</v>
       </c>
       <c r="L5">
-        <v>5.046067864158219</v>
+        <v>7.086105761015729</v>
+      </c>
+      <c r="N5">
+        <v>2.040037896857511</v>
       </c>
       <c r="O5">
         <v>0.0004114379757251</v>
@@ -955,7 +967,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L6">
-        <v>3.212634617501281</v>
+        <v>5.217874426565914</v>
+      </c>
+      <c r="N6">
+        <v>2.005239809064632</v>
       </c>
       <c r="O6">
         <v>0.0020571898786257</v>
@@ -1008,7 +1023,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L7">
-        <v>4.215378442319276</v>
+        <v>6.44680582203762</v>
+      </c>
+      <c r="N7">
+        <v>2.231427379718343</v>
       </c>
       <c r="O7">
         <v>0.0370294178152643</v>
@@ -1061,7 +1079,10 @@
         <v>8.1</v>
       </c>
       <c r="L8">
-        <v>12.67875797281028</v>
+        <v>15.44085619137003</v>
+      </c>
+      <c r="N8">
+        <v>2.762098218559743</v>
       </c>
       <c r="O8">
         <v>1.226085167660975</v>
@@ -1114,7 +1135,10 @@
         <v>7.7</v>
       </c>
       <c r="L9">
-        <v>241.5315874550092</v>
+        <v>408.9973849582377</v>
+      </c>
+      <c r="N9">
+        <v>167.4657975032285</v>
       </c>
       <c r="O9">
         <v>6.418432421312487</v>
@@ -1167,7 +1191,10 @@
         <v>7.8</v>
       </c>
       <c r="L10">
-        <v>116.9828894181631</v>
+        <v>197.6709554879005</v>
+      </c>
+      <c r="N10">
+        <v>80.68806606973737</v>
       </c>
       <c r="O10">
         <v>3.077556058424193</v>
@@ -1220,7 +1247,10 @@
         <v>7.9</v>
       </c>
       <c r="L11">
-        <v>226.7063575286032</v>
+        <v>385.6901211323176</v>
+      </c>
+      <c r="N11">
+        <v>158.9837636037144</v>
       </c>
       <c r="O11">
         <v>6.08928204073236</v>
@@ -1273,7 +1303,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L12">
-        <v>5.512947992763777</v>
+        <v>6.404648992456293</v>
+      </c>
+      <c r="N12">
+        <v>0.8917009996925155</v>
       </c>
       <c r="O12">
         <v>0.9216210656243572</v>
@@ -1326,7 +1359,10 @@
         <v>8.4</v>
       </c>
       <c r="L13">
-        <v>4.695215994399442</v>
+        <v>7.126732378926838</v>
+      </c>
+      <c r="N13">
+        <v>2.431516384527395</v>
       </c>
       <c r="O13">
         <v>0.1016251800041143</v>
@@ -1379,7 +1415,10 @@
         <v>8.1</v>
       </c>
       <c r="L14">
-        <v>9.461442472636064</v>
+        <v>11.41013538903727</v>
+      </c>
+      <c r="N14">
+        <v>1.948692916401204</v>
       </c>
       <c r="O14">
         <v>1.152026332030446</v>
@@ -1432,7 +1471,10 @@
         <v>7.9</v>
       </c>
       <c r="L15">
-        <v>27.74759034816682</v>
+        <v>30.55318617646767</v>
+      </c>
+      <c r="N15">
+        <v>2.805595828300841</v>
       </c>
       <c r="O15">
         <v>3.094013577453199</v>
@@ -1485,7 +1527,10 @@
         <v>7.2</v>
       </c>
       <c r="L16">
-        <v>8.352424356630296</v>
+        <v>10.94923165817386</v>
+      </c>
+      <c r="N16">
+        <v>2.596807301543569</v>
       </c>
       <c r="O16">
         <v>0.9010491668380992</v>
@@ -1538,7 +1583,10 @@
         <v>6.8</v>
       </c>
       <c r="L17">
-        <v>19.52129313577917</v>
+        <v>20.04761421364647</v>
+      </c>
+      <c r="N17">
+        <v>0.5263210778672895</v>
       </c>
       <c r="O17">
         <v>1.748611396831928</v>
@@ -1591,7 +1639,10 @@
         <v>7.8</v>
       </c>
       <c r="L18">
-        <v>2.928942406120034</v>
+        <v>6.582741624372292</v>
+      </c>
+      <c r="N18">
+        <v>3.653799218252257</v>
       </c>
       <c r="O18">
         <v>0.0074058835630528</v>
@@ -1644,7 +1695,10 @@
         <v>6.8</v>
       </c>
       <c r="L19">
-        <v>3.373030094925314</v>
+        <v>8.096870512808591</v>
+      </c>
+      <c r="N19">
+        <v>4.723840417883276</v>
       </c>
       <c r="O19">
         <v>0.0032915038058012</v>
@@ -1697,7 +1751,10 @@
         <v>6.9</v>
       </c>
       <c r="L20">
-        <v>104.1068229728117</v>
+        <v>158.4788351491846</v>
+      </c>
+      <c r="N20">
+        <v>54.37201217637289</v>
       </c>
       <c r="O20">
         <v>1.349516560378523</v>
@@ -1750,7 +1807,10 @@
         <v>7.2</v>
       </c>
       <c r="L21">
-        <v>9.324340883196797</v>
+        <v>10.40743136575014</v>
+      </c>
+      <c r="N21">
+        <v>1.083090482553348</v>
       </c>
       <c r="O21">
         <v>0.8228759514503189</v>
@@ -1803,7 +1863,10 @@
         <v>7.3</v>
       </c>
       <c r="L22">
-        <v>311.6929336394225</v>
+        <v>505.2572969873101</v>
+      </c>
+      <c r="N22">
+        <v>193.5643633478875</v>
       </c>
       <c r="O22">
         <v>11.1088253445793</v>
@@ -1856,7 +1919,10 @@
         <v>7.2</v>
       </c>
       <c r="L23">
-        <v>64.27812901163207</v>
+        <v>107.166772216355</v>
+      </c>
+      <c r="N23">
+        <v>42.88864320472294</v>
       </c>
       <c r="O23">
         <v>3.04464102036618</v>
@@ -1909,7 +1975,10 @@
         <v>7.2</v>
       </c>
       <c r="L24">
-        <v>323.3219642677102</v>
+        <v>557.1216166261137</v>
+      </c>
+      <c r="N24">
+        <v>233.7996523584034</v>
       </c>
       <c r="O24">
         <v>10.28594939312899</v>
@@ -1962,7 +2031,10 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>8.455346242388275</v>
+        <v>8.555390744792801</v>
+      </c>
+      <c r="N25">
+        <v>0.1000445024045261</v>
       </c>
       <c r="O25">
         <v>1.324830281835014</v>
@@ -2015,7 +2087,10 @@
         <v>7.1</v>
       </c>
       <c r="L26">
-        <v>11.93295157652457</v>
+        <v>15.37361250704544</v>
+      </c>
+      <c r="N26">
+        <v>3.440660930520876</v>
       </c>
       <c r="O26">
         <v>1.201398889117466</v>
@@ -2065,7 +2140,10 @@
         <v>7.7</v>
       </c>
       <c r="L27">
-        <v>6.047448197627157</v>
+        <v>7.748204738504101</v>
+      </c>
+      <c r="N27">
+        <v>1.700756540876944</v>
       </c>
       <c r="O27">
         <v>0.4443530137831722</v>
@@ -2118,7 +2196,10 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>2.305316454020718</v>
+        <v>5.476292204146787</v>
+      </c>
+      <c r="N28">
+        <v>3.170975750126068</v>
       </c>
       <c r="O28">
         <v>0.0012343139271754</v>
@@ -2171,7 +2252,10 @@
         <v>8</v>
       </c>
       <c r="L29">
-        <v>2.488444687981949</v>
+        <v>5.520228086936502</v>
+      </c>
+      <c r="N29">
+        <v>3.031783398954552</v>
       </c>
       <c r="O29">
         <v>0.0016457519029006</v>
@@ -2224,7 +2308,10 @@
         <v>6.9</v>
       </c>
       <c r="L30">
-        <v>3.257911142450076</v>
+        <v>4.201809273831909</v>
+      </c>
+      <c r="N30">
+        <v>0.9438981313818334</v>
       </c>
       <c r="O30">
         <v>0.2666118082699033</v>
@@ -2277,7 +2364,10 @@
         <v>7.7</v>
       </c>
       <c r="L31">
-        <v>2.963117002744867</v>
+        <v>6.4733741088515</v>
+      </c>
+      <c r="N31">
+        <v>3.510257106106634</v>
       </c>
       <c r="O31">
         <v>0.0098745114174038</v>
@@ -2330,7 +2420,10 @@
         <v>7.8</v>
       </c>
       <c r="L32">
-        <v>4.074732611431488</v>
+        <v>7.406649517599618</v>
+      </c>
+      <c r="N32">
+        <v>3.33191690616813</v>
       </c>
       <c r="O32">
         <v>0.0185147089076321</v>
